--- a/outputs/daily/hr_rankings_2026-08-08_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-08_full.xlsx
@@ -6102,34 +6102,30 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8050,34 +8046,30 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9438,34 +9430,30 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -11384,28 +11372,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr"/>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="Y40" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11662,34 +11654,30 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -15810,34 +15798,30 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 1</t>
-        </is>
-      </c>
+      <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -18300,28 +18284,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W65" t="inlineStr"/>
-      <c r="X65" t="inlineStr"/>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="Y65" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -35154,34 +35142,30 @@
       </c>
       <c r="W126" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X126" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y126" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB126" t="inlineStr"/>
       <c r="AC126" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -47588,28 +47572,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W171" t="inlineStr"/>
-      <c r="X171" t="inlineStr"/>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X171" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Y171" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z171" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB171" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB171" t="inlineStr"/>
       <c r="AC171" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -78512,34 +78500,30 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
